--- a/光伏配储项目/电价数据/2026/兴瑶站.xlsx
+++ b/光伏配储项目/电价数据/2026/兴瑶站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.51039</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38706</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7432300000000001</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.57098</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.57931</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.49938</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43757</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45439</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44062</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42326</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42029</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40883</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39823</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40022</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.3849</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40213</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.4231</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41255</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35455</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39148</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38494</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41694</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39208</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42068</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.4139</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42389</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44406</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.36036</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.28626</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29507</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30899</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.29591</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.31024</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.11684</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.09520000000000001</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.10382</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.09009</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.11376</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.0483</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.09656999999999999</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.12243</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.13099</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.1287</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08996999999999999</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.11289</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.06898</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.01661</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.15251</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21664</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25692</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.30628</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.21237</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.10285</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.00644</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.14294</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.31286</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.26893</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.3065</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.18828</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.56099</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.4244</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.4927</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.9736399999999999</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39938</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.59388</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.44347</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44583</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.42874</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.5680299999999999</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.44925</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.60222</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.79855</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.63644</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.6170099999999999</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.73434</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.88495</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.42139</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.6626299999999999</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.62627</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.68772</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.6208899999999999</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.61827</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.63506</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.6051799999999999</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.46835</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48917</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.39943</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.4163</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42598</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.6898300000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.78981</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.78377</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.25457</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.85064</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5278099999999999</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51903</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5053299999999999</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50726</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48947</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40065</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47017</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37915</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38016</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39127</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33697</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37042</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37524</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37521</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35923</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38015</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41937</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.50043</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.59677</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.69614</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42993</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.36967</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.41735</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34776</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.41194</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.5067200000000001</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.15971</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29913</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.04375</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.35597</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.35704</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.3728</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.48875</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.7952</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.97341</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.36794</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.37137</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.39633</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.81331</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.49421</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.35605</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.11027</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28212</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.37841</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.31438</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.4748</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.26392</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.26004</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.26997</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.4811</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.41378</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.2912</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.39139</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.35564</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.55872</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.6871499999999999</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.5321699999999999</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.68667</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.7573099999999999</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.7617</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.54604</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.51738</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.82672</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.5071600000000001</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.42634</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.97322</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.37542</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.4688</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.6200599999999999</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44419</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43771</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.42218</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.38095</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33464</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32148</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.53734</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.53489</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.4284</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38389</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.4052</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.41879</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39008</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38917</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36767</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43785</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45456</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33845</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37079</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39627</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.3718</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35591</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35171</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36687</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35909</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38479</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47385</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45432</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.4486</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40115</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35302</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37146</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.46686</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.38199</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.38311</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.19958</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.49372</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.26772</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.31835</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31774</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.30125</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34332</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.46694</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.40026</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.50148</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.47456</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.39438</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.29285</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.14859</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.25472</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.30389</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.28409</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.27784</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29335</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29991</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.3821</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.43781</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.40412</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.45653</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.42875</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.46915</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.60489</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.36784</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.38095</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.33874</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.5177999999999999</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.60182</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.55083</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.58896</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.4561</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.41696</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.47427</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.40082</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.45412</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.43416</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.45493</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.44101</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.39117</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.37114</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.41549</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.39543</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.39396</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.3972</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36304</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.3425</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31933</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.38575</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.41408</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.36296</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.35827</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.33275</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.32568</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.3242</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46085</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.32982</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.32407</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.32424</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.33184</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.31046</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.30676</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.30238</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.30688</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33359</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35475</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.35667</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38946</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.3343</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.34379</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.35716</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.29893</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.27777</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.30514</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.12478</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.20324</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.16488</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.33692</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.26829</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.25648</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30434</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.5000899999999999</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.43616</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.33729</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.07239</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.06398</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.14288</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.28124</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.16534</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.18369</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.51135</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.05518</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.12369</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.21219</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.23141</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.38232</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.34498</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.29933</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.22327</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.24198</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.2097</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.26869</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.13986</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.2577</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.2754</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.30079</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33785</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.3723</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.41961</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.58173</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.45448</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.43559</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.36266</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.35413</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.36267</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.32726</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.33764</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.30891</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31705</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32492</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29627</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.30891</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.29905</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29743</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.3006</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.38433</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38232</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35648</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33895</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30112</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31134</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30835</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30646</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.2918</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30578</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30736</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.29181</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.29606</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.2901</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.2901</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29012</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29803</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29208</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29507</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31234</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30635</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33277</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32617</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27917</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26026</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.05404999999999999</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04446</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.05401</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.0561</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04421</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04617</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.05136</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04679999999999999</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.03607</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04752</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04762</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04334</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04291</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04264</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04296</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04276</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.042</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04325</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04629</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04464</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04269</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04296</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04661</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04485</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04837</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21898</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04593999999999999</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.05159</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05543</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.04825</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.00262</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.16097</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.05593</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.11348</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29009</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.2938</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29366</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33538</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33399</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38642</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39209</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38745</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.39259</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.41691</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39982</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.43862</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46756</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40005</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41716</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.35301</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35539</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35099</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36801</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.6806</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40015</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44628</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42341</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42343</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35839</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33322</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.3093399999999999</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.3579</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35443</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33504</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31517</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33534</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30015</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33534</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35203</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31605</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04338</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04688000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04564</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04608</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04608</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04608</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04543999999999999</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04377</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04042</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04348</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10393</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.00156</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04303</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04365</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04367</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04368</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04555</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04542</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04542</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04344</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04308</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04528</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04311</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04279</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04514</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04508</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04522</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04403</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04306</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04498</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04454</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04998</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04727000000000001</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04761</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20022</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14304</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29043</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29515</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30502</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.3003</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29539</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29324</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.2939</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29287</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29732</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29118</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29534</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26919</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29423</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29844</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30881</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30425</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30232</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.3147799999999999</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31882</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36681</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33579</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31812</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40491</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32101</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30755</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31499</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.3017</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28148</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29486</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29111</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28837</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27149</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27128</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28137</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17261</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15886</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1712</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14793</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15966</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15884</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23654</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21425</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.2268</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26924</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28607</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29109</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31969</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29111</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28137</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27098</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28124</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31059</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30535</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31671</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30969</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.2955</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38322</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38022</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42783</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45465</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41784</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41465</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38916</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40188</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30098</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29928</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15661</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29358</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31327</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34596</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50766</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62203</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78101</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92037</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49455</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91673</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8706199999999999</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.30045</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.36135</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.8951399999999999</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6329400000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.19461</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8724700000000001</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5470900000000001</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33854</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03821</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53849</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7975</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5304800000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77954</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78274</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87758</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87729</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49927</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.40466</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.40783</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.45697</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21493</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.8791599999999999</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55122</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62971</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54031</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49999</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45683</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42523</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43858</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45036</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39019</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45284</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.4203</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35289</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40008</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36531</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38714</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41487</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43388</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34395</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39046</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34922</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40478</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45089</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35475</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40022</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40018</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58684</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42791</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59614</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.6022000000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66596</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41763</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5795800000000001</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45094</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8771</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.63198</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8694</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.85146</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.8618899999999999</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44095</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32982</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30566</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.34252</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.47127</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29649</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.29918</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31113</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35725</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33278</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31792</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30627</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31914</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31508</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29924</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31377</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.3122200000000001</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31522</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.31012</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32247</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32365</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32493</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35458</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34096</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34028</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33745</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41015</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41279</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45254</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41515</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39165</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37511</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35346</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.92625</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36055</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.4677</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.36821</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.42404</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.48177</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38331</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40994</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36733</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.37588</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.3563</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34889</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38912</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50024</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35718</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38776</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35533</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37074</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36311</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31655</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31367</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.3327</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33823</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31184</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30431</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28997</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.2811</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16539</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.3017</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30235</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.31977</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29714</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26211</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19932</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27726</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.20031</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31394</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27756</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31145</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31197</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31365</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31082</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30447</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31184</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29358</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31064</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29015</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30739</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.31792</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31307</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29003</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34749</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25563</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.28684</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27635</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34037</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38569</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43465</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.29934</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42321</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44827</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42052</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40181</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40054</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59702</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.89025</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.2974</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.10849</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.68549</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7712</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6352599999999999</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.56996</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.44481</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44495</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.49259</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43452</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43224</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.4107</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.40866</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.41887</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.49278</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.40866</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.42894</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.40916</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.42816</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38709</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42324</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.44471</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39274</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4188</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.42908</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.40866</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.40865</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.39661</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.41894</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.37007</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.39666</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49112</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34384</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29663</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36413</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.36552</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30966</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.34154</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30696</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30242</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.34782</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.57486</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.37335</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.32503</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25047</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.27811</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.5825499999999999</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.41346</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.30303</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.29591</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.38978</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30279</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26211</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25665</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30663</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28165</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28573</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.30364</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29311</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.3124</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31299</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32084</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31453</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.39919</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.39664</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.37032</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.36123</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.37057</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36283</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.57485</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.45824</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.74215</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.45848</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.4374</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37525</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42228</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38598</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36897</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32417</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31855</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.41924</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33901</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33501</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32564</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32567</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32556</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.31978</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30975</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32402</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.38774</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39702</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.3727200000000001</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35263</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33372</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.28184</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33223</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.2974</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.31293</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.25788</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.29805</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.24253</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.15663</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.16086</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29186</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.16791</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.09079000000000001</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.15749</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.15098</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.15233</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.1509</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.15318</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.28225</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.15914</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.29139</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.27343</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.15801</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.17266</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.12316</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.11022</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.16254</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.15131</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.15602</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.29418</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.30294</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.33563</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.37164</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.3766600000000001</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34511</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.3945</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35827</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38229</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44525</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39748</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.38818</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.39921</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39515</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.43896</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43525</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4346</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.43931</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.43945</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.39956</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38806</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39535</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.38943</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35891</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34769</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34896</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33926</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5301399999999999</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38578</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46165</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.41869</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41108</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.37683</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3767</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.38923</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37669</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36745</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37741</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.38781</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.3678</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.37743</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35376</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33895</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35349</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.3678</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.37736</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34709</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36083</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29873</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30595</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29055</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.2818</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.26808</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26417</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.19788</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30679</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24831</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24101</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26806</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29803</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28537</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30764</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30099</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.32352</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29229</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.2823</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24034</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31323</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30239</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.31487</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30366</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28373</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31592</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33213</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32708</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32793</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.32837</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34068</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34473</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36513</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.37171</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.35559</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.39228</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.25032</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.36053</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35445</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41835</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.3616</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36608</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37543</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.37858</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.37878</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38338</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35894</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.37179</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.44525</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37012</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.40223</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38862</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36413</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34167</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34688</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34498</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.35702</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33783</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34857</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33048</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33217</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.3449</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36556</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31262</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33916</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32576</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33499</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32393</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.30568</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.39386</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.30563</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.4053</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.45884</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.32663</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.45615</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.30371</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.29505</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.37496</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.00715</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.28349</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25014</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.29815</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.11113</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.22168</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.25351</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.29834</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.29564</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.27944</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.30314</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.31464</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.31145</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.32108</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.35286</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.35198</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.41635</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.34315</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.34506</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31791</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.38671</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32807</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.33428</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.34202</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.33926</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.43974</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.49277</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.71149</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36498</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.38758</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.32143</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.32314</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.26385</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.38188</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30441</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.32809</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.30323</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30824</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.30338</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.28746</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32284</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.38288</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33497</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33017</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32528</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32527</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32568</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32402</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32824</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32685</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32402</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33058</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33515</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32105</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32096</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34096</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34656</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32104</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31724</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34099</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.30125</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.35622</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34443</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31339</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.3303</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.2848</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.3185</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.34065</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32022</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31451</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.30915</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.32595</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36335</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34439</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.3319</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34726</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37575</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36879</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36106</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36709</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.3622</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37238</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36207</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.3952</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38738</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37113</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35478</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.39642</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.38472</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36092</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.36047</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.3496</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35145</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.36072</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.35444</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.37088</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.35525</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.35821</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33703</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34614</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34617</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.3824</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34614</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.34257</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34618</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.35821</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.35821</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.34217</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.33968</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.33223</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.35637</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33297</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33861</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30405</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32607</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32726</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31753</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31727</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31723</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31675</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.3666</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31768</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32998</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32226</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32304</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33239</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33684</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34452</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35767</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.37745</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.36094</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35302</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35374</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36492</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35845</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34544</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35832</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36027</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38114</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38054</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38461</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.44097</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40951</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.39564</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37792</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.69892</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.7663099999999999</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.48359</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.33244</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45518</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39292</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35936</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.36034</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.37019</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.35216</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.42024</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37763</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37095</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36216</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.3621</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.3689</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36033</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35906</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35294</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36035</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.36051</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35209</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.35227</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.3703</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35874</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.39429</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36558</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38306</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35644</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35087</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.36724</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31972</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32681</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26561</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14807</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30212</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28529</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28423</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19947</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.2581</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.2803</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31618</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28007</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.21821</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.26177</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28506</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27824</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29147</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32217</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.1498</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29273</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.29874</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34935</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33491</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.3332</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33267</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.36122</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34681</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.36077</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43416</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38419</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.42132</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.5932000000000001</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.67073</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.7012999999999999</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.48701</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.74178</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.53604</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.89761</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.47149</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.4832</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40762</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.38243</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.48356</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43036</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.43392</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.38061</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37475</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36003</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3436</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49094</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.50689</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.5101600000000001</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.4231</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.40532</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40917</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41751</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40964</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41954</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39867</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39935</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41528</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.4049</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39231</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38502</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41451</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38504</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41931</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38733</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40204</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40204</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41433</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40439</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.44468</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45768</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5599299999999999</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.49248</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.44491</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.6120099999999999</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.4675299999999999</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.44448</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.35771</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.39221</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.38605</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.41913</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.42838</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.52744</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.47179</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.29846</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.36661</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.37118</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.38312</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.40273</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.28924</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.32874</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.33242</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.36951</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.64159</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.36701</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.15688</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.28287</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.33655</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.31393</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33242</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.34306</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35457</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35433</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.35866</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35346</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.38165</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.40979</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.43333</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.4862</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43448</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.5059399999999999</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.54767</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.62121</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.80204</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.82029</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.86146</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.69713</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.80584</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.60748</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.5625399999999999</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.95348</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.87395</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.63301</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.71697</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.45779</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47309</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.51293</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47778</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.49943</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41799</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5696599999999999</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42886</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44345</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.47171</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.45997</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.43463</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.45885</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.43647</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39997</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.47317</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39801</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40731</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.41199</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38676</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37843</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37348</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36464</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.39778</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39001</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.38929</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.37278</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36656</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.38928</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.40958</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36902</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.39627</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39605</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.4063</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.3959</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36863</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34461</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33859</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.37719</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.18293</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.38141</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.33947</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40494</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.44494</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.38827</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46359</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31214</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.11037</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.1806</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.29934</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29479</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35239</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34849</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.3723</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.37932</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37404</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38414</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41625</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36962</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.42916</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41315</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41329</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38228</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.37683</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38493</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39043</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40887</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40882</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.3455299999999999</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37335</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37669</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.4122</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.38915</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.40204</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37489</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36464</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39522</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.38032</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36543</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44466</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39392</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39369</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35658</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37881</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37793</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35709</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35804</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35473</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35855</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34604</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.3512</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33499</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33762</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30494</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.31687</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.27262</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31503</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30931</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22758</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28806</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23053</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28797</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25018</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25305</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13981</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29286</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29892</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.31217</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.24923</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25123</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.16939</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18109</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27214</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30932</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30872</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.22838</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.24903</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26257</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23284</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27577</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28427</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28386</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32807</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30819</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35279</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34782</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35204</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.35961</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37348</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35669</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35798</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.38018</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35532</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36937</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36969</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37022</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34513</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36448</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37962</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36371</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36855</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34826</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35029</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32522</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34358</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33853</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32349</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31857</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30836</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.3088399999999999</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31376</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31005</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31106</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30595</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30595</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30839</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30589</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30525</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30595</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30644</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29006</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.25674</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.24373</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.16735</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.20618</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.2144</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01794</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00045</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.0295</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04956</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.10767</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.01693</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03954999999999999</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04957</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.02011</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.0425</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04028</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04852</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04815</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02653</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.03006</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.13459</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04944</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00285</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.28937</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04943</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.03395</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04957</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04953</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04325</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.1706</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.19681</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.23603</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27973</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.26431</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.26594</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.26423</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.26975</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.28451</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.30479</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.29224</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.29154</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28036</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30819</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30056</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.30694</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29087</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.30511</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.28912</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30422</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.29581</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.32398</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.4064700000000001</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33283</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.30957</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.29087</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.29124</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.28389</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.2816</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29495</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.13817</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.56787</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.16203</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.29044</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.28619</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.25719</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.30132</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.3054</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.28707</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.27193</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.2487</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.23826</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.26454</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.25532</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.22162</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.24794</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.2477</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.27733</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.27017</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.27207</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.25146</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.29932</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.27435</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.31003</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.36631</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.30716</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.27782</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.27835</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.2284</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.1594</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.63537</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.6309400000000001</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.65462</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.57359</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.16148</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.30368</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.09248999999999999</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.23746</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.17689</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.12016</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.12807</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.08239</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.2281</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.11025</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.31237</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.03549</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.04525999999999999</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.10039</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.17535</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.02645</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.11937</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.12559</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.14682</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.01792</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.10254</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.11004</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.11088</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.14304</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25492</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29327</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.27515</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32474</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33212</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35439</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.35853</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.3716</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.33745</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.38148</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.37654</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.4079700000000001</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37157</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.37118</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.36063</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35397</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36397</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37525</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.33273</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32358</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.3739</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.35661</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32907</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33949</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33647</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32776</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.35214</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.02913</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.3287</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.31582</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33408</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.33853</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33379</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.49319</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.57064</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.38061</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.42658</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.29784</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.41121</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.43875</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.47834</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.3939</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.47063</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.39068</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.38007</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.44533</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31165</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14033</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27532</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27011</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30522</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.27385</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.30473</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31139</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29162</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31244</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32697</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.3256</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32349</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34381</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34587</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33459</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35774</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.35692</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36305</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37926</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31023</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.47143</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35603</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.42564</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35644</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.37827</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.37006</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35699</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36807</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31023</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33578</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32082</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33443</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37235</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.28273</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32897</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33351</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.30898</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35336</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33573</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33103</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.37823</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36925</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35838</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35239</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.39578</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.6508700000000001</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.61927</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.5425399999999999</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37402</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.37112</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.3547</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35682</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.30612</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.34769</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.40315</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35249</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31076</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.30889</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33492</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26107</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33486</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.3472</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32799</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.28115</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28402</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.33529</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.35439</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.36294</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.41651</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39751</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.5158400000000001</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.5311900000000001</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.46102</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.4756</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.41535</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.48086</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.37821</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.41072</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.41618</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.35074</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.36109</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.37544</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.38269</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.38134</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.36916</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.38738</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41665</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.4401</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.40129</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.38478</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.48935</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.41827</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.39374</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.41905</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.38001</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37261</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.58489</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.3778</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34701</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.47887</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.37559</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.37558</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.35701</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37518</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.3741</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37848</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37687</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36885</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36673</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36129</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35957</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35539</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32753</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35608</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36456</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37825</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.41351</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.38407</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.37019</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35966</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.39411</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.41512</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.37891</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.36862</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43923</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.38375</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.37944</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.29105</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35464</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31941</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36699</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.26802</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35458</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.36095</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29407</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31111</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.32967</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.31477</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33669</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.3444</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.34201</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.3048</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.38449</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.3763</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.38566</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36456</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.39094</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.4746</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.39963</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.45562</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.43084</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.43173</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.5223099999999999</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.60825</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.60763</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.44904</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.58294</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.52366</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.57437</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.5287500000000001</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.39948</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.5720299999999999</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.49031</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.11103</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.9334199999999999</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.62702</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.61787</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.41217</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.46841</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.41516</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.38315</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37749</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37507</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.3819</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.26632</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36961</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36671</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33712</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34818</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33654</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.35615</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33855</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.31696</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32689</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.31977</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31752</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.32047</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31909</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.31114</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36985</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.32678</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.31286</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30762</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30269</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.2982</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.29402</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.31102</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.23611</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.26624</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.13737</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.23173</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.17216</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.06032</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.32391</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.1546</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.02902</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.19687</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.16306</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.00036</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.29831</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.25792</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.15586</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.05496</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.05147</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.06587</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.15088</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.07307</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.05472999999999999</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.16949</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.1424</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.16352</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.26613</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.30025</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.29768</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.28211</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.36791</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.35204</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.37256</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.35256</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.3638</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.25487</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.3576</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.30655</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.39063</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.38315</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.41818</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.39002</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39424</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42955</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39634</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.39771</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.43451</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.38991</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.45363</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.40103</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.3928</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.37469</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.5952200000000001</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.38111</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34622</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.99224</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.36765</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.48437</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.4264</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.38069</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.34239</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.38145</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37809</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38069</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.35693</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34821</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37632</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36146</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.37969</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38598</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35749</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36346</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36199</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36443</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34973</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38324</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34358</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33563</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.30807</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.31229</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.32325</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.31157</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.2965</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.26775</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.26153</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.27594</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.26144</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.11324</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.01807</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.01834</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.0178</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.04294</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.1688</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.04114</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00542</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01848</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04627000000000001</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.0169</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.01613</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.16443</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.26746</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.04533</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.23925</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.15954</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.25384</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.28839</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32132</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.30886</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.33423</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.32048</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.33812</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.48521</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.41546</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.40631</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37194</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.38983</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36501</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34328</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.39664</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5814900000000001</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.66489</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38586</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.3777</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39458</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.39818</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.37341</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.40736</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.35492</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.40342</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.43096</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.38531</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.36939</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.37345</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.36638</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36283</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.37505</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.62679</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.38571</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.38758</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.3698</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.36306</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36641</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.35391</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.44672</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.35283</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39384</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3809</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35839</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33711</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33926</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33763</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.3409700000000001</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34665</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.35397</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.31497</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.2815</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.25811</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.23178</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.14478</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.2087</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.23232</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.11482</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.15166</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.03447</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.00195</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04697</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.0475</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04641</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04679</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04499</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.0418</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.07934000000000001</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.02914</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.06387</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.09756999999999999</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.17199</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.19642</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.12131</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.26004</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.23023</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.12446</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.04768</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.26371</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.14759</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.11761</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.23725</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.18751</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.24125</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.24587</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.20547</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.24707</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.27758</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.27917</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.30211</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.30661</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.3098399999999999</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.31375</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.34812</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.32719</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.3576</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38672</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37242</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37875</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.38728</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38881</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.40161</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.41215</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.51925</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40126</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.4156</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.41477</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.40535</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38209</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.39332</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.41341</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38244</v>
       </c>
     </row>
   </sheetData>
